--- a/IA_CCBS_BANK_SIDE/Customer/CCBS_GetIndividualCustomer.xlsx
+++ b/IA_CCBS_BANK_SIDE/Customer/CCBS_GetIndividualCustomer.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aafent\Desktop\IA\Interfaces\IA_CCBS_BANK_SIDE\Customer\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kmilos\source\repos\iApply_CCBS_API\IA_CCBS_BANK_SIDE\Customer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EC21BCD-DF65-464A-8364-F08F0DBA4AE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF0F64E1-6995-4FBB-920C-2AF6B28B3BD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-7800" windowWidth="29040" windowHeight="16440" xr2:uid="{5318078F-747C-4C31-9481-48B8478D2881}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{5318078F-747C-4C31-9481-48B8478D2881}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="3" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="232">
   <si>
     <t>Financial Sector</t>
   </si>
@@ -748,6 +748,60 @@
   </si>
   <si>
     <t>Model</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>AMLFields</t>
+  </si>
+  <si>
+    <t>estTransLevel</t>
+  </si>
+  <si>
+    <t>fundsSD</t>
+  </si>
+  <si>
+    <t>Estimated Transaction Level</t>
+  </si>
+  <si>
+    <t>string[]</t>
+  </si>
+  <si>
+    <t>Funds Source / Destination - multiple selection field</t>
+  </si>
+  <si>
+    <t>polExp</t>
+  </si>
+  <si>
+    <t>Political exposure</t>
+  </si>
+  <si>
+    <t>busRelPurpose</t>
+  </si>
+  <si>
+    <t>typeOfProduct</t>
+  </si>
+  <si>
+    <t>repRisk</t>
+  </si>
+  <si>
+    <t>Reputation Risk</t>
+  </si>
+  <si>
+    <t>Business Relation Purpose</t>
+  </si>
+  <si>
+    <t>type of product</t>
+  </si>
+  <si>
+    <t>clientStatus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Client status </t>
+  </si>
+  <si>
+    <t>Class with next fields in extended categories</t>
   </si>
 </sst>
 </file>
@@ -841,7 +895,7 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -861,9 +915,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -878,12 +929,6 @@
   </cellStyles>
   <dxfs count="16">
     <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -896,7 +941,13 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -944,34 +995,34 @@
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{4A550235-21B5-4EAC-86DB-D3404736C2D4}" name="Seq." dataDxfId="13"/>
     <tableColumn id="2" xr3:uid="{1CB7858A-D8BA-4363-BACF-F1D23AFB0BAE}" name="Description" dataDxfId="12"/>
-    <tableColumn id="6" xr3:uid="{2093AA3A-5E08-4A76-946C-9176E9B3E631}" name="Model" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{B6748203-7F20-45D6-A5EB-C846A5ABB334}" name="iApply" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{49416A76-918B-4569-94E9-C3865B13BFA4}" name="Data Type" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{CABDE198-A767-4C4C-9ECA-178576282B19}" name="Notes" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{2093AA3A-5E08-4A76-946C-9176E9B3E631}" name="Model" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{B6748203-7F20-45D6-A5EB-C846A5ABB334}" name="iApply" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{49416A76-918B-4569-94E9-C3865B13BFA4}" name="Data Type" dataDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{CABDE198-A767-4C4C-9ECA-178576282B19}" name="Notes" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{9724DFF8-9BD5-41D3-921E-8D10475D90D0}" name="Table2" displayName="Table2" ref="B2:G91" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
-  <autoFilter ref="B2:G91" xr:uid="{9724DFF8-9BD5-41D3-921E-8D10475D90D0}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{9724DFF8-9BD5-41D3-921E-8D10475D90D0}" name="Table2" displayName="Table2" ref="B2:G100" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
+  <autoFilter ref="B2:G100" xr:uid="{9724DFF8-9BD5-41D3-921E-8D10475D90D0}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{25BE5662-06A6-4C14-96AE-14514FFD07A3}" name="Seq." dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{C6EC2B8A-8F9B-4C2D-903C-E7D34359EF58}" name="Description" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{4BA315EC-31DA-4F6C-8622-565CC9700F66}" name="Model" dataDxfId="0"/>
-    <tableColumn id="3" xr3:uid="{685D3D59-DADC-476B-B2BC-6E64F8D69AE2}" name="iApply" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{BEB5D1C5-31AE-449D-9A33-1D0BA0DB2FDC}" name="Data Type" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{3D144780-2FD8-4B59-BB8A-F44EE55C258A}" name="Notes" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{25BE5662-06A6-4C14-96AE-14514FFD07A3}" name="Seq." dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{C6EC2B8A-8F9B-4C2D-903C-E7D34359EF58}" name="Description" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{4BA315EC-31DA-4F6C-8622-565CC9700F66}" name="Model" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{685D3D59-DADC-476B-B2BC-6E64F8D69AE2}" name="iApply" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{BEB5D1C5-31AE-449D-9A33-1D0BA0DB2FDC}" name="Data Type" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{3D144780-2FD8-4B59-BB8A-F44EE55C258A}" name="Notes" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1009,7 +1060,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1115,7 +1166,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1257,7 +1308,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1266,20 +1317,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0370CE2C-15CC-482B-AC42-9F7F42D23E30}">
   <dimension ref="B2:C15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="1"/>
+    <col min="1" max="1" width="9.109375" style="1"/>
     <col min="2" max="2" width="12" style="1" customWidth="1"/>
-    <col min="3" max="3" width="60.140625" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="1"/>
+    <col min="3" max="3" width="60.109375" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C2" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
         <v>195</v>
       </c>
@@ -1287,7 +1338,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
         <v>197</v>
       </c>
@@ -1295,7 +1346,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
         <v>198</v>
       </c>
@@ -1303,7 +1354,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
         <v>211</v>
       </c>
@@ -1311,11 +1362,11 @@
         <v>212</v>
       </c>
     </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B7" s="2"/>
       <c r="C7" s="3"/>
     </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B8" s="2" t="s">
         <v>199</v>
       </c>
@@ -1323,11 +1374,11 @@
         <v>200</v>
       </c>
     </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B9" s="2"/>
       <c r="C9" s="3"/>
     </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B10" s="2" t="s">
         <v>201</v>
       </c>
@@ -1335,7 +1386,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B11" s="2" t="s">
         <v>203</v>
       </c>
@@ -1343,15 +1394,15 @@
         <v>205</v>
       </c>
     </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B12" s="2"/>
       <c r="C12" s="3"/>
     </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B13" s="2"/>
       <c r="C13" s="3"/>
     </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B14" s="2" t="s">
         <v>204</v>
       </c>
@@ -1359,7 +1410,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B15" s="2"/>
       <c r="C15" s="3"/>
     </row>
@@ -1371,19 +1422,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{628E527F-A3A2-4740-9E10-2ECFE7A0147E}">
   <dimension ref="B1:G4"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.28515625" style="4" customWidth="1"/>
-    <col min="3" max="4" width="25.85546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="24.140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="4.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.33203125" style="4" customWidth="1"/>
+    <col min="3" max="4" width="25.88671875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="24.109375" style="1" customWidth="1"/>
     <col min="6" max="6" width="17" style="1" customWidth="1"/>
     <col min="7" max="7" width="25" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="1"/>
+    <col min="8" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B2" s="4" t="s">
         <v>208</v>
       </c>
@@ -1403,7 +1454,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B3" s="4">
         <v>1</v>
       </c>
@@ -1417,7 +1468,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B4" s="4">
         <v>2</v>
       </c>
@@ -1442,20 +1493,20 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B9FF4B3-3E3D-4272-B782-E7DFED979819}">
-  <dimension ref="B2:G94"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B2:G99"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="4"/>
+    <col min="1" max="1" width="2.5546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" style="4"/>
     <col min="3" max="3" width="27" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="27" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.28515625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="86.5703125" style="8" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="1"/>
+    <col min="5" max="5" width="13.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.33203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="86.5546875" style="7" customWidth="1"/>
+    <col min="8" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="4" t="s">
         <v>208</v>
       </c>
@@ -1471,11 +1522,11 @@
       <c r="F2" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="7" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B3" s="4">
         <v>1</v>
       </c>
@@ -1486,7 +1537,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B4" s="4">
         <v>2</v>
       </c>
@@ -1500,7 +1551,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B5" s="4">
         <v>3</v>
       </c>
@@ -1514,7 +1565,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B6" s="4">
         <v>4</v>
       </c>
@@ -1528,7 +1579,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B7" s="4">
         <v>5</v>
       </c>
@@ -1542,7 +1593,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B8" s="4">
         <v>6</v>
       </c>
@@ -1553,7 +1604,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B9" s="4">
         <v>7</v>
       </c>
@@ -1567,7 +1618,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B10" s="4">
         <v>8</v>
       </c>
@@ -1581,7 +1632,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B11" s="4">
         <v>9</v>
       </c>
@@ -1595,7 +1646,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B12" s="4">
         <v>10</v>
       </c>
@@ -1606,7 +1657,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B13" s="4">
         <v>11</v>
       </c>
@@ -1620,7 +1671,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B14" s="4">
         <v>12</v>
       </c>
@@ -1633,11 +1684,11 @@
       <c r="F14" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="G14" s="8" t="s">
+      <c r="G14" s="7" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B15" s="4">
         <v>13</v>
       </c>
@@ -1651,7 +1702,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B16" s="4">
         <v>14</v>
       </c>
@@ -1662,7 +1713,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B17" s="4">
         <v>15</v>
       </c>
@@ -1676,7 +1727,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B18" s="4">
         <v>16</v>
       </c>
@@ -1689,11 +1740,11 @@
       <c r="F18" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="G18" s="8" t="s">
+      <c r="G18" s="7" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B19" s="4">
         <v>17</v>
       </c>
@@ -1707,7 +1758,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B20" s="4">
         <v>18</v>
       </c>
@@ -1720,11 +1771,11 @@
       <c r="F20" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="G20" s="8" t="s">
+      <c r="G20" s="7" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="21" spans="2:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B21" s="4">
         <v>19</v>
       </c>
@@ -1737,11 +1788,11 @@
       <c r="F21" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G21" s="8" t="s">
+      <c r="G21" s="7" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="22" spans="2:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B22" s="4">
         <v>20</v>
       </c>
@@ -1754,11 +1805,11 @@
       <c r="F22" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G22" s="8" t="s">
+      <c r="G22" s="7" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B23" s="4">
         <v>21</v>
       </c>
@@ -1772,7 +1823,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B24" s="4">
         <v>22</v>
       </c>
@@ -1786,7 +1837,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B25" s="4">
         <v>23</v>
       </c>
@@ -1800,7 +1851,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="26" spans="2:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B26" s="4">
         <v>24</v>
       </c>
@@ -1813,11 +1864,11 @@
       <c r="F26" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G26" s="8" t="s">
+      <c r="G26" s="7" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B27" s="4">
         <v>25</v>
       </c>
@@ -1828,10 +1879,10 @@
         <v>92</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.25">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B28" s="4">
         <v>26</v>
       </c>
@@ -1845,7 +1896,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="2:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B29" s="4">
         <v>27</v>
       </c>
@@ -1858,11 +1909,11 @@
       <c r="F29" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="G29" s="8" t="s">
+      <c r="G29" s="7" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B30" s="4">
         <v>28</v>
       </c>
@@ -1876,7 +1927,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B31" s="4">
         <v>29</v>
       </c>
@@ -1890,7 +1941,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B32" s="4">
         <v>30</v>
       </c>
@@ -1901,7 +1952,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B33" s="4">
         <v>31</v>
       </c>
@@ -1912,7 +1963,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B34" s="4">
         <v>32</v>
       </c>
@@ -1926,7 +1977,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B35" s="4">
         <v>33</v>
       </c>
@@ -1940,7 +1991,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B36" s="4">
         <v>34</v>
       </c>
@@ -1953,11 +2004,11 @@
       <c r="F36" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="G36" s="8" t="s">
+      <c r="G36" s="7" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="37" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B37" s="4">
         <v>35</v>
       </c>
@@ -1971,7 +2022,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="38" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B38" s="4">
         <v>36</v>
       </c>
@@ -1985,7 +2036,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="39" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B39" s="4">
         <v>37</v>
       </c>
@@ -1995,11 +2046,11 @@
       <c r="F39" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="G39" s="8" t="s">
+      <c r="G39" s="7" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B40" s="4">
         <v>38</v>
       </c>
@@ -2013,7 +2064,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B41" s="4">
         <v>39</v>
       </c>
@@ -2027,13 +2078,13 @@
         <v>118</v>
       </c>
     </row>
-    <row r="42" spans="2:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B42" s="4">
         <v>40</v>
       </c>
       <c r="G42" s="6"/>
     </row>
-    <row r="43" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B43" s="4">
         <v>41</v>
       </c>
@@ -2047,7 +2098,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B44" s="4">
         <v>42</v>
       </c>
@@ -2061,7 +2112,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B45" s="4">
         <v>43</v>
       </c>
@@ -2075,7 +2126,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B46" s="4">
         <v>44</v>
       </c>
@@ -2089,7 +2140,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B47" s="4">
         <v>45</v>
       </c>
@@ -2100,7 +2151,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="48" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B48" s="4">
         <v>46</v>
       </c>
@@ -2114,7 +2165,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B49" s="4">
         <v>47</v>
       </c>
@@ -2125,7 +2176,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B50" s="4">
         <v>48</v>
       </c>
@@ -2138,11 +2189,11 @@
       <c r="F50" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G50" s="8" t="s">
+      <c r="G50" s="7" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="51" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B51" s="4">
         <v>49</v>
       </c>
@@ -2156,7 +2207,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="52" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B52" s="4">
         <v>50</v>
       </c>
@@ -2170,7 +2221,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B53" s="4">
         <v>51</v>
       </c>
@@ -2184,7 +2235,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="54" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B54" s="4">
         <v>52</v>
       </c>
@@ -2195,7 +2246,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="55" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B55" s="4">
         <v>53</v>
       </c>
@@ -2206,7 +2257,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="56" spans="2:7" ht="257.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:7" ht="257.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="4">
         <v>54</v>
       </c>
@@ -2216,11 +2267,11 @@
       <c r="E56" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G56" s="9" t="s">
+      <c r="G56" s="8" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="57" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B57" s="4">
         <v>55</v>
       </c>
@@ -2231,7 +2282,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="58" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B58" s="4">
         <v>56</v>
       </c>
@@ -2245,7 +2296,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="59" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B59" s="4">
         <v>57</v>
       </c>
@@ -2259,7 +2310,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="60" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B60" s="4">
         <v>58</v>
       </c>
@@ -2270,7 +2321,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="61" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B61" s="4">
         <v>59</v>
       </c>
@@ -2284,7 +2335,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="62" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B62" s="4">
         <v>60</v>
       </c>
@@ -2298,7 +2349,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B63" s="4">
         <v>61</v>
       </c>
@@ -2311,11 +2362,11 @@
       <c r="F63" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="G63" s="8" t="s">
+      <c r="G63" s="7" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="64" spans="2:7" ht="150" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:7" ht="129.6" x14ac:dyDescent="0.3">
       <c r="B64" s="4">
         <v>62</v>
       </c>
@@ -2325,11 +2376,11 @@
       <c r="F64" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="G64" s="8" t="s">
+      <c r="G64" s="7" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="65" spans="2:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B65" s="4">
         <v>63</v>
       </c>
@@ -2339,11 +2390,11 @@
       <c r="F65" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="G65" s="8" t="s">
+      <c r="G65" s="7" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="66" spans="2:7" ht="150" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:7" ht="144" x14ac:dyDescent="0.3">
       <c r="B66" s="4">
         <v>64</v>
       </c>
@@ -2356,11 +2407,11 @@
       <c r="F66" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="G66" s="8" t="s">
+      <c r="G66" s="7" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="67" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B67" s="4">
         <v>65</v>
       </c>
@@ -2374,7 +2425,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="68" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B68" s="4">
         <v>66</v>
       </c>
@@ -2388,7 +2439,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="69" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B69" s="4">
         <v>67</v>
       </c>
@@ -2402,7 +2453,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="70" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B70" s="4">
         <v>68</v>
       </c>
@@ -2416,7 +2467,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="71" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B71" s="4">
         <v>69</v>
       </c>
@@ -2430,7 +2481,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="72" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B72" s="4">
         <v>70</v>
       </c>
@@ -2444,7 +2495,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="73" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B73" s="4">
         <v>71</v>
       </c>
@@ -2458,7 +2509,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="74" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B74" s="4">
         <v>72</v>
       </c>
@@ -2472,7 +2523,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="75" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B75" s="4">
         <v>73</v>
       </c>
@@ -2486,7 +2537,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B76" s="4">
         <v>74</v>
       </c>
@@ -2500,7 +2551,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="77" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B77" s="4">
         <v>75</v>
       </c>
@@ -2514,7 +2565,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="78" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B78" s="4">
         <v>76</v>
       </c>
@@ -2528,7 +2579,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="79" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B79" s="4">
         <v>77</v>
       </c>
@@ -2542,7 +2593,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="80" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B80" s="4">
         <v>78</v>
       </c>
@@ -2556,7 +2607,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="81" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B81" s="4">
         <v>79</v>
       </c>
@@ -2570,7 +2621,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="82" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B82" s="4">
         <v>80</v>
       </c>
@@ -2584,7 +2635,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="83" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B83" s="4">
         <v>81</v>
       </c>
@@ -2598,7 +2649,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="84" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B84" s="4">
         <v>82</v>
       </c>
@@ -2612,7 +2663,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="85" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B85" s="4">
         <v>83</v>
       </c>
@@ -2626,7 +2677,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="86" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B86" s="4">
         <v>84</v>
       </c>
@@ -2640,7 +2691,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="87" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B87" s="4">
         <v>85</v>
       </c>
@@ -2654,7 +2705,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="88" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B88" s="4">
         <v>86</v>
       </c>
@@ -2668,7 +2719,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="89" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B89" s="4">
         <v>87</v>
       </c>
@@ -2682,7 +2733,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="90" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B90" s="4">
         <v>88</v>
       </c>
@@ -2696,7 +2747,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="91" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B91" s="4">
         <v>89</v>
       </c>
@@ -2710,29 +2761,121 @@
         <v>2</v>
       </c>
     </row>
-    <row r="92" spans="2:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B92" s="7"/>
-      <c r="C92" s="1"/>
+    <row r="92" spans="2:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B92" s="4">
+        <v>90</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>215</v>
+      </c>
       <c r="D92" s="1"/>
       <c r="E92" s="1"/>
       <c r="F92" s="1"/>
-      <c r="G92" s="8"/>
-    </row>
-    <row r="93" spans="2:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B93" s="7"/>
-      <c r="C93" s="1"/>
+      <c r="G92" s="7" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="93" spans="2:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B93" s="4">
+        <v>91</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>216</v>
+      </c>
       <c r="D93" s="1"/>
-      <c r="E93" s="1"/>
+      <c r="E93" s="1" t="s">
+        <v>214</v>
+      </c>
       <c r="F93" s="1"/>
-      <c r="G93" s="8"/>
-    </row>
-    <row r="94" spans="2:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B94" s="7"/>
-      <c r="C94" s="1"/>
+      <c r="G93" s="7" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="94" spans="2:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B94" s="4">
+        <v>92</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>217</v>
+      </c>
       <c r="D94" s="1"/>
-      <c r="E94" s="1"/>
+      <c r="E94" s="1" t="s">
+        <v>219</v>
+      </c>
       <c r="F94" s="1"/>
-      <c r="G94" s="8"/>
+      <c r="G94" s="7" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="95" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B95" s="4">
+        <v>93</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="G95" s="7" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="96" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B96" s="4">
+        <v>94</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="G96" s="7" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="97" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B97" s="4">
+        <v>95</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="G97" s="7" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="98" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B98" s="4">
+        <v>96</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="G98" s="7" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="99" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B99" s="4">
+        <v>97</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="G99" s="7" t="s">
+        <v>230</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2752,14 +2895,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="5f05de3e-e8ee-428b-b91d-f2173b3e9a74" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001EFB7DDC95092145A7794BE0B7D697A4" ma:contentTypeVersion="7" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="5744b9113a61f730a5188ccc510a726c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="5f05de3e-e8ee-428b-b91d-f2173b3e9a74" xmlns:ns4="a0aed20c-369f-4a18-8454-6e01f2c67c75" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ff8cd097ea52a8868cabb10b709355a5" ns3:_="" ns4:_="">
     <xsd:import namespace="5f05de3e-e8ee-428b-b91d-f2173b3e9a74"/>
@@ -2942,6 +3077,14 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="5f05de3e-e8ee-428b-b91d-f2173b3e9a74" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34E3B460-67AD-43B5-BAAD-BA10DDE2781A}">
   <ds:schemaRefs>
@@ -2951,23 +3094,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7DD77BB5-D96B-40DB-BE3A-8FC814F678ED}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="a0aed20c-369f-4a18-8454-6e01f2c67c75"/>
-    <ds:schemaRef ds:uri="5f05de3e-e8ee-428b-b91d-f2173b3e9a74"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2A2336B-8201-4736-BEF3-8E4BC5C434D5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2984,4 +3110,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7DD77BB5-D96B-40DB-BE3A-8FC814F678ED}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="a0aed20c-369f-4a18-8454-6e01f2c67c75"/>
+    <ds:schemaRef ds:uri="5f05de3e-e8ee-428b-b91d-f2173b3e9a74"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>